--- a/JogosAdicionais.xlsx
+++ b/JogosAdicionais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.miranda\Desktop\Tips\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFFD6F9-B844-46D0-945F-2C92DD8CA438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9C5F8A4-9F77-46B1-AAA8-EC4A0E6B1948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Div</t>
   </si>
@@ -40,13 +40,10 @@
     <t>E0</t>
   </si>
   <si>
-    <t>17:30:00</t>
-  </si>
-  <si>
-    <t>Sp Lisbon</t>
-  </si>
-  <si>
-    <t>Guimaraes</t>
+    <t>Paris SG</t>
+  </si>
+  <si>
+    <t>Marseille</t>
   </si>
 </sst>
 </file>
@@ -108,12 +105,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,16 +447,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>46028</v>
-      </c>
-      <c r="C2" t="s">
+        <v>46029</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
